--- a/RAWDATA/obs_data_corr_5500_4900.xlsx
+++ b/RAWDATA/obs_data_corr_5500_4900.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/a048908_unipi_it/Documents/R/CHRONOS/NEWCODE/RAWDATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="13_ncr:1_{E2EEF40C-AD1E-4144-A088-5AC700FB87E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08D41D7F-BE7E-488C-8CE1-7D24B37AFF01}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{149EAF83-2471-4D82-89DC-F2F731B50AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9548733F-8D8F-4421-9133-33FB462E50ED}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2591AB75-0193-49A9-968E-8CA7C48823ED}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="113">
   <si>
     <t>Grotta Sant'Angelo II</t>
   </si>
@@ -89,9 +89,6 @@
     <t>Fornace Cappuccini</t>
   </si>
   <si>
-    <t>Pian di Calisti</t>
-  </si>
-  <si>
     <t>Savignano sul Panaro</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>Fiorano Modenese</t>
   </si>
   <si>
-    <t>Balsignano </t>
-  </si>
-  <si>
     <t>Grotta Scaloria</t>
   </si>
   <si>
@@ -329,18 +323,6 @@
     <t>Lineare tosco-laziale Cf.</t>
   </si>
   <si>
-    <t>Cuccuru is Arrius</t>
-  </si>
-  <si>
-    <t>AA-80543</t>
-  </si>
-  <si>
-    <t>PCRD</t>
-  </si>
-  <si>
-    <t>Cardial</t>
-  </si>
-  <si>
     <t>Krivače</t>
   </si>
   <si>
@@ -384,6 +366,15 @@
   </si>
   <si>
     <t>Kronio</t>
+  </si>
+  <si>
+    <t>Balsignano II</t>
+  </si>
+  <si>
+    <t>Bande rosse</t>
+  </si>
+  <si>
+    <t>Piani di Calisti</t>
   </si>
 </sst>
 </file>
@@ -435,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -462,9 +453,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -815,15 +803,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C157A01-C199-4D3F-9904-F5AD72692F22}">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.08984375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="9" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="9" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="8.81640625" style="1"/>
     <col min="8" max="8" width="13.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" style="1"/>
+    <col min="9" max="9" width="8.81640625" style="1"/>
     <col min="10" max="10" width="10.08984375" style="10" customWidth="1"/>
     <col min="11" max="12" width="8.90625" style="10"/>
     <col min="13" max="13" width="8.90625" style="3"/>
@@ -838,71 +826,71 @@
   <sheetData>
     <row r="1" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="D1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="K1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="N1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="13">
         <v>8.9739000000000004</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="13">
         <v>42.331299999999999</v>
       </c>
       <c r="D2" s="7">
@@ -924,44 +912,35 @@
         <v>1</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M2" s="8">
         <v>5498</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>0</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0</v>
-      </c>
-      <c r="S2" s="3">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="13">
         <v>12.086119999999999</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="13">
         <v>43.069180000000003</v>
       </c>
       <c r="D3" s="7">
@@ -983,25 +962,25 @@
         <v>8</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M3" s="8">
         <v>5498</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q3" s="3">
         <v>1</v>
@@ -1017,10 +996,10 @@
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="13">
         <v>17.616931000000001</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="13">
         <v>40.498820000000002</v>
       </c>
       <c r="D4" s="7">
@@ -1042,25 +1021,25 @@
         <v>1499</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M4" s="8">
         <v>5490</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Q4" s="3">
         <v>1</v>
@@ -1076,50 +1055,50 @@
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="13">
         <v>10.083299999999999</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <v>42.58</v>
       </c>
       <c r="D5" s="7">
         <v>84</v>
       </c>
-      <c r="E5" s="7">
-        <v>99</v>
-      </c>
-      <c r="F5" s="7">
-        <v>138</v>
-      </c>
-      <c r="G5" s="7">
-        <v>15</v>
-      </c>
-      <c r="H5" s="7">
-        <v>25</v>
+      <c r="E5" s="2">
+        <v>102</v>
+      </c>
+      <c r="F5" s="2">
+        <v>131</v>
+      </c>
+      <c r="G5" s="2">
+        <v>3</v>
+      </c>
+      <c r="H5" s="2">
+        <v>46</v>
       </c>
       <c r="I5" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M5" s="8">
         <v>5472</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q5" s="3">
         <v>1</v>
@@ -1135,10 +1114,10 @@
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="13">
         <v>15.34183</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <v>41.491540000000001</v>
       </c>
       <c r="D6" s="7">
@@ -1160,75 +1139,75 @@
         <v>9</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M6" s="8">
         <v>5461</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>12.2745</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <v>42.104399999999998</v>
       </c>
       <c r="D7" s="7">
         <v>39</v>
       </c>
       <c r="E7" s="7">
-        <v>847</v>
+        <v>951</v>
       </c>
       <c r="F7" s="7">
-        <v>186</v>
+        <v>288</v>
       </c>
       <c r="G7" s="7">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H7" s="7">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="I7" s="7">
-        <v>1179</v>
+        <v>1309</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M7" s="8">
         <v>5443</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Q7" s="3">
         <v>1</v>
@@ -1244,10 +1223,10 @@
       <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <v>15.9178</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="13">
         <v>37.9392</v>
       </c>
       <c r="D8" s="7">
@@ -1269,25 +1248,25 @@
         <v>703</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M8" s="8">
         <v>5432</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q8" s="4">
         <v>1</v>
@@ -1296,17 +1275,17 @@
         <v>0</v>
       </c>
       <c r="S8" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="14">
+        <v>20</v>
+      </c>
+      <c r="B9" s="13">
         <v>13.531877</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="13">
         <v>41.948729999999998</v>
       </c>
       <c r="D9" s="7">
@@ -1328,35 +1307,35 @@
         <v>17</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M9" s="3">
         <v>5422</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="13">
         <v>13.57343</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="13">
         <v>43.56373</v>
       </c>
       <c r="D10" s="7">
@@ -1378,31 +1357,31 @@
         <v>4</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M10" s="8">
         <v>5421</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
       </c>
       <c r="R10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="3">
         <v>0</v>
@@ -1412,10 +1391,10 @@
       <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>15.750553</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="13">
         <v>41.61289</v>
       </c>
       <c r="D11" s="7">
@@ -1437,25 +1416,25 @@
         <v>43</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M11" s="8">
         <v>5359</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q11" s="3">
         <v>1</v>
@@ -1469,12 +1448,12 @@
     </row>
     <row r="12" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="14">
+        <v>27</v>
+      </c>
+      <c r="B12" s="13">
         <v>15.912000000000001</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="13">
         <v>41.636699999999998</v>
       </c>
       <c r="D12" s="7">
@@ -1496,35 +1475,44 @@
         <v>11</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M12" s="3">
         <v>5340</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>1</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>9.3773800000000005</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="13">
         <v>42.68974</v>
       </c>
       <c r="D13" s="7">
@@ -1546,7 +1534,7 @@
         <v>117</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K13" s="10">
         <v>6420</v>
@@ -1558,13 +1546,13 @@
         <v>5340</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Q13" s="4">
         <v>0</v>
@@ -1580,10 +1568,10 @@
       <c r="A14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="13">
         <v>14.39301</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13">
         <v>42.224980000000002</v>
       </c>
       <c r="D14" s="7">
@@ -1605,25 +1593,25 @@
         <v>13</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M14" s="8">
         <v>5301</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1637,12 +1625,12 @@
     </row>
     <row r="15" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="14">
+        <v>17</v>
+      </c>
+      <c r="B15" s="13">
         <v>11.034610000000001</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13">
         <v>44.475960000000001</v>
       </c>
       <c r="D15" s="7">
@@ -1664,35 +1652,35 @@
         <v>1</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M15" s="3">
         <v>5291</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="14">
+        <v>28</v>
+      </c>
+      <c r="B16" s="13">
         <v>8.5597989999999999</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13">
         <v>39.207129999999999</v>
       </c>
       <c r="D16" s="7">
@@ -1714,25 +1702,25 @@
         <v>84</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M16" s="3">
         <v>5079</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P16" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q16" s="4">
         <v>0</v>
@@ -1748,10 +1736,10 @@
       <c r="A17" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="13">
         <v>16.672481999999999</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="13">
         <v>40.674019999999999</v>
       </c>
       <c r="D17" s="7">
@@ -1773,7 +1761,7 @@
         <v>40</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K17" s="9">
         <v>6301</v>
@@ -1785,26 +1773,32 @@
         <v>5269</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>1</v>
+      </c>
+      <c r="R17" s="4">
+        <v>0</v>
+      </c>
+      <c r="S17" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="13">
         <v>11.872712</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13">
         <v>44.283430000000003</v>
       </c>
       <c r="D18" s="7">
@@ -1814,37 +1808,37 @@
         <v>167</v>
       </c>
       <c r="F18" s="7">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="G18" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" s="7">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="I18" s="7">
         <v>306</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M18" s="8">
         <v>5268</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="Q18" s="3">
         <v>1</v>
@@ -1858,12 +1852,12 @@
     </row>
     <row r="19" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="13">
+        <v>95</v>
+      </c>
+      <c r="B19" s="12">
         <v>15.84</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="12">
         <v>43.86</v>
       </c>
       <c r="D19" s="2">
@@ -1885,25 +1879,25 @@
         <v>3</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M19" s="3">
         <v>5225</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q19" s="3">
         <v>1</v>
@@ -1917,12 +1911,12 @@
     </row>
     <row r="20" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="14">
+        <v>112</v>
+      </c>
+      <c r="B20" s="13">
         <v>12.948956000000001</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13">
         <v>43.252200000000002</v>
       </c>
       <c r="D20" s="7">
@@ -1944,35 +1938,44 @@
         <v>6</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M20" s="3">
         <v>5217</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>1</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="14">
+        <v>29</v>
+      </c>
+      <c r="B21" s="13">
         <v>8.5525300000000009</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="13">
         <v>39.688229999999997</v>
       </c>
       <c r="D21" s="7">
@@ -1994,57 +1997,66 @@
         <v>764</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M21" s="3">
         <v>5207</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="13">
         <v>13.9621</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13">
         <v>42.221899999999998</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <v>27</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="11">
         <v>3</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="11">
         <v>3</v>
       </c>
-      <c r="G22" s="12">
-        <v>0</v>
-      </c>
-      <c r="H22" s="12">
-        <v>0</v>
-      </c>
-      <c r="I22" s="12">
+      <c r="G22" s="11">
+        <v>0</v>
+      </c>
+      <c r="H22" s="11">
+        <v>0</v>
+      </c>
+      <c r="I22" s="11">
         <v>6</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K22" s="10">
         <v>6247</v>
@@ -2056,23 +2068,23 @@
         <v>5186</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="14">
+        <v>89</v>
+      </c>
+      <c r="B23" s="13">
         <v>11.6767</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13">
         <v>43.078699999999998</v>
       </c>
       <c r="D23" s="7">
@@ -2094,35 +2106,44 @@
         <v>5</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M23" s="3">
         <v>5185</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>1</v>
+      </c>
+      <c r="R23" s="3">
+        <v>1</v>
+      </c>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="14">
+        <v>25</v>
+      </c>
+      <c r="B24" s="13">
         <v>10.361458000000001</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="13">
         <v>43.556579999999997</v>
       </c>
       <c r="D24" s="7">
@@ -2144,7 +2165,7 @@
         <v>24</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K24" s="10">
         <v>6040</v>
@@ -2156,13 +2177,13 @@
         <v>5185</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2178,10 +2199,10 @@
       <c r="A25" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="13">
         <v>13.626537000000001</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="13">
         <v>42.754550000000002</v>
       </c>
       <c r="D25" s="7">
@@ -2203,35 +2224,44 @@
         <v>1</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M25" s="8">
         <v>5179</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>12</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>1</v>
+      </c>
+      <c r="R25" s="3">
+        <v>1</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="13">
         <v>14.0832</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="13">
         <v>42.374499999999998</v>
       </c>
       <c r="D26" s="7">
@@ -2253,35 +2283,44 @@
         <v>5</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M26" s="8">
         <v>5179</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>12</v>
       </c>
+      <c r="Q26" s="3">
+        <v>1</v>
+      </c>
+      <c r="R26" s="3">
+        <v>1</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B27" s="13">
+        <v>96</v>
+      </c>
+      <c r="B27" s="12">
         <v>16.146000000000001</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="12">
         <v>43.832999999999998</v>
       </c>
       <c r="D27" s="2">
@@ -2303,25 +2342,25 @@
         <v>19</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M27" s="3">
         <v>5135</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q27" s="3">
         <v>1</v>
@@ -2337,47 +2376,47 @@
       <c r="A28" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="13">
         <v>13.943842999999999</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13">
         <v>42.342669999999998</v>
       </c>
       <c r="D28" s="7">
         <v>13</v>
       </c>
-      <c r="E28" s="7">
-        <v>195</v>
-      </c>
-      <c r="F28" s="7">
-        <v>138</v>
-      </c>
-      <c r="G28" s="7">
-        <v>49</v>
-      </c>
-      <c r="H28" s="7">
-        <v>0</v>
+      <c r="E28" s="2">
+        <v>307</v>
+      </c>
+      <c r="F28" s="2">
+        <v>199</v>
+      </c>
+      <c r="G28" s="2">
+        <v>54</v>
+      </c>
+      <c r="H28" s="2">
+        <v>72</v>
       </c>
       <c r="I28" s="7">
-        <v>382</v>
+        <v>632</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="M28" s="12">
+        <v>39</v>
+      </c>
+      <c r="M28" s="11">
         <v>5125.1581770010416</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>12</v>
@@ -2394,12 +2433,12 @@
     </row>
     <row r="29" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" s="13">
+        <v>97</v>
+      </c>
+      <c r="B29" s="12">
         <v>15.99</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="12">
         <v>43.7</v>
       </c>
       <c r="D29" s="2">
@@ -2421,25 +2460,25 @@
         <v>73</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M29" s="4">
         <v>5124</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q29" s="3">
         <v>1</v>
@@ -2453,12 +2492,12 @@
     </row>
     <row r="30" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="14">
+        <v>22</v>
+      </c>
+      <c r="B30" s="13">
         <v>13.987246000000001</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13">
         <v>42.430349999999997</v>
       </c>
       <c r="D30" s="7">
@@ -2480,22 +2519,22 @@
         <v>128</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M30" s="3">
         <v>5093</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>12</v>
@@ -2507,63 +2546,63 @@
         <v>1</v>
       </c>
       <c r="S30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="14">
+        <v>110</v>
+      </c>
+      <c r="B31" s="13">
         <v>16.721499999999999</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13">
         <v>41.069600000000001</v>
       </c>
       <c r="D31" s="7">
         <v>88</v>
       </c>
-      <c r="E31" s="7">
-        <v>17</v>
-      </c>
-      <c r="F31" s="7">
-        <v>15</v>
-      </c>
-      <c r="G31" s="7">
-        <v>1</v>
-      </c>
-      <c r="H31" s="7">
-        <v>0</v>
-      </c>
-      <c r="I31" s="7">
-        <v>33</v>
+      <c r="E31" s="2">
+        <v>2</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>13</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M31" s="3">
-        <v>5084</v>
+        <v>4849</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="Q31" s="3">
         <v>1</v>
       </c>
       <c r="R31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" s="3">
         <v>0</v>
@@ -2571,12 +2610,12 @@
     </row>
     <row r="32" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="14">
+        <v>21</v>
+      </c>
+      <c r="B32" s="13">
         <v>17.083549999999999</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="13">
         <v>43.003689999999999</v>
       </c>
       <c r="D32" s="7">
@@ -2598,44 +2637,35 @@
         <v>3</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M32" s="3">
         <v>5046</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>1</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B33" s="14">
+        <v>24</v>
+      </c>
+      <c r="B33" s="13">
         <v>15.540967</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="13">
         <v>41.452629999999999</v>
       </c>
       <c r="D33" s="7">
@@ -2657,35 +2687,44 @@
         <v>4</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M33" s="3">
         <v>5036</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>1</v>
+      </c>
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" s="14">
+        <v>19</v>
+      </c>
+      <c r="B34" s="13">
         <v>10.0938</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="13">
         <v>42.589640000000003</v>
       </c>
       <c r="D34" s="7">
@@ -2707,25 +2746,25 @@
         <v>231</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M34" s="3">
         <v>5119</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
@@ -2739,12 +2778,12 @@
     </row>
     <row r="35" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B35" s="14">
+        <v>23</v>
+      </c>
+      <c r="B35" s="13">
         <v>5.6444000000000001</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="13">
         <v>45.221699999999998</v>
       </c>
       <c r="D35" s="7">
@@ -2766,25 +2805,25 @@
         <v>1</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M35" s="3">
         <v>4983</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O35" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Q35" s="3">
         <v>0</v>
@@ -2798,12 +2837,12 @@
     </row>
     <row r="36" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B36" s="14">
+        <v>86</v>
+      </c>
+      <c r="B36" s="13">
         <v>8.3282799999999995</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="13">
         <v>44.162300000000002</v>
       </c>
       <c r="D36" s="7">
@@ -2825,25 +2864,25 @@
         <v>21</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M36" s="3">
         <v>5077</v>
       </c>
       <c r="N36" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P36" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P36" s="10" t="s">
-        <v>89</v>
       </c>
       <c r="Q36" s="3">
         <v>0</v>
@@ -2857,12 +2896,12 @@
     </row>
     <row r="37" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B37" s="14">
+        <v>18</v>
+      </c>
+      <c r="B37" s="13">
         <v>16.157499999999999</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="13">
         <v>39.779899999999998</v>
       </c>
       <c r="D37" s="7">
@@ -2884,25 +2923,25 @@
         <v>148</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M37" s="3">
         <v>4928</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q37" s="3">
         <v>1</v>
@@ -2916,12 +2955,12 @@
     </row>
     <row r="38" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="14">
+        <v>26</v>
+      </c>
+      <c r="B38" s="13">
         <v>10.823464</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="13">
         <v>44.544110000000003</v>
       </c>
       <c r="D38" s="7">
@@ -2943,35 +2982,44 @@
         <v>4</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M38" s="3">
         <v>4925</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>1</v>
+      </c>
+      <c r="R38" s="3">
+        <v>0</v>
+      </c>
+      <c r="S38" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39" s="14">
+        <v>93</v>
+      </c>
+      <c r="B39" s="13">
         <v>8.507104</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="13">
         <v>39.720056</v>
       </c>
       <c r="D39" s="2">
@@ -2993,25 +3041,25 @@
         <v>1421</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M39" s="8">
         <v>4796.0116763827837</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O39" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q39" s="3">
         <v>0</v>
@@ -3023,83 +3071,83 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B40" s="14">
-        <v>8.5029950000000003</v>
-      </c>
-      <c r="C40" s="14">
-        <v>39.920392</v>
-      </c>
-      <c r="D40" s="2">
-        <v>68</v>
-      </c>
-      <c r="E40" s="2">
-        <v>29</v>
-      </c>
-      <c r="F40" s="2">
-        <v>1981</v>
-      </c>
-      <c r="G40" s="2">
-        <v>9</v>
-      </c>
-      <c r="H40" s="2">
-        <v>26</v>
-      </c>
-      <c r="I40" s="2">
-        <v>2045</v>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="13">
+        <v>15.785299999999999</v>
+      </c>
+      <c r="C40" s="13">
+        <v>41.526299999999999</v>
+      </c>
+      <c r="D40" s="7">
+        <v>51</v>
+      </c>
+      <c r="E40" s="7">
+        <v>4</v>
+      </c>
+      <c r="F40" s="7">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7">
+        <v>0</v>
+      </c>
+      <c r="I40" s="7">
+        <v>4</v>
       </c>
       <c r="J40" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="K40" s="10">
+        <v>6520</v>
+      </c>
+      <c r="L40" s="10">
+        <v>70</v>
+      </c>
+      <c r="M40" s="3">
+        <v>5620</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O40" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="P40" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K40" s="10">
-        <v>6040</v>
-      </c>
-      <c r="L40" s="10">
-        <v>80</v>
-      </c>
-      <c r="M40" s="8">
-        <v>4729</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="O40" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="P40" s="6" t="s">
-        <v>100</v>
-      </c>
       <c r="Q40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="3">
         <v>0</v>
       </c>
       <c r="S40" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>106</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="B41" s="14">
-        <v>15.785299999999999</v>
-      </c>
-      <c r="C41" s="14">
-        <v>41.526299999999999</v>
+        <v>16.875664</v>
+      </c>
+      <c r="C41" s="12">
+        <v>42.945019000000002</v>
       </c>
       <c r="D41" s="7">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="E41" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="7">
         <v>0</v>
@@ -3108,66 +3156,57 @@
         <v>0</v>
       </c>
       <c r="I41" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="K41" s="10">
-        <v>6520</v>
-      </c>
-      <c r="L41" s="10">
-        <v>70</v>
+        <v>37</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L41" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="M41" s="3">
-        <v>5620</v>
+        <v>5140</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="O41" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="P41" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>1</v>
-      </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B42" s="15">
-        <v>16.875664</v>
-      </c>
-      <c r="C42" s="13">
-        <v>42.945019000000002</v>
-      </c>
-      <c r="D42" s="7">
-        <v>119</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1</v>
-      </c>
-      <c r="F42" s="7">
-        <v>2</v>
-      </c>
-      <c r="G42" s="7">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7">
-        <v>3</v>
-      </c>
-      <c r="I42" s="7">
-        <v>3</v>
+      <c r="B42" s="12">
+        <v>14.700283000000001</v>
+      </c>
+      <c r="C42" s="12">
+        <v>37.332642</v>
+      </c>
+      <c r="D42" s="2">
+        <v>128</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
+        <v>9</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2">
+        <v>9</v>
       </c>
       <c r="J42" s="10" t="s">
         <v>39</v>
@@ -3179,16 +3218,16 @@
         <v>39</v>
       </c>
       <c r="M42" s="3">
-        <v>5140</v>
+        <v>5191</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>79</v>
+        <v>85</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="P42" s="10" t="s">
+        <v>109</v>
       </c>
       <c r="Q42" s="3">
         <v>1</v>
@@ -3201,71 +3240,12 @@
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B43" s="13">
-        <v>14.700283000000001</v>
-      </c>
-      <c r="C43" s="13">
-        <v>37.332642</v>
-      </c>
-      <c r="D43" s="2">
-        <v>128</v>
-      </c>
-      <c r="E43" s="2">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2">
-        <v>9</v>
-      </c>
-      <c r="G43" s="2">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2">
-        <v>0</v>
-      </c>
-      <c r="I43" s="2">
-        <v>9</v>
-      </c>
-      <c r="J43" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="K43" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="M43" s="3">
-        <v>5191</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="P43" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>1</v>
-      </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S43">
-    <sortCondition descending="1" ref="M2:M43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S42">
+    <sortCondition descending="1" ref="M2:M42"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
